--- a/astro-site/public/dl/seafood-restaurant-checklist-templates/03-seafood-haccp-traceability-shellfish-tags.xlsx
+++ b/astro-site/public/dl/seafood-restaurant-checklist-templates/03-seafood-haccp-traceability-shellfish-tags.xlsx
@@ -916,7 +916,7 @@
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="9" t="n"/>
     </row>
-    <row r="18" ht="68" customHeight="1">
+    <row r="18" ht="81.75" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>CCP 1</t>
@@ -924,7 +924,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Receiving: fresh fish at 41 °F or below, frozen at 0 °F or below and frozen solid; shellstock per NSSP rules (on ice, or shipped at 45 °F air or 50 °F internal or below), then held at 41 °F (FDA Food Code 3-202.11)</t>
+          <t>Receiving: fresh fish at 41 °F or below; frozen food received frozen solid (0 °F or below is the common target); shellstock per NSSP rules (on ice, or shipped at 45 °F air or 50 °F internal or below), then held at 41 °F (FDA Food Code 3-202.11)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -968,7 +968,7 @@
       <c r="E19" s="6" t="inlineStr"/>
       <c r="F19" s="6" t="inlineStr"/>
     </row>
-    <row r="20" ht="20" customHeight="1">
+    <row r="20" ht="41" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>CCP 3</t>
@@ -976,7 +976,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Cooking: fish and shellfish to 145 °F for 15 s internal (FDA Food Code 3-401.11)</t>
+          <t>Cooking: whole fish and shellfish to 145 °F for 15 s internal; comminuted fish 155 °F for 17 s; stuffed fish 165 °F (FDA Food Code 3-401.11)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -992,7 +992,7 @@
       <c r="E20" s="6" t="inlineStr"/>
       <c r="F20" s="6" t="inlineStr"/>
     </row>
-    <row r="21" ht="20" customHeight="1">
+    <row r="21" ht="54.5" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>CCP 4</t>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Display: seafood on drained ice at 41 °F or below (FDA Food Code 3-501.16), rotate every 2 h</t>
+          <t>Display: seafood on drained ice at 41 °F or below (FDA Food Code 3-501.16): ice replenished every 90 min, melt water drained every 60 min, product rotated every 2 h</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1016,7 +1016,7 @@
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
     </row>
-    <row r="22" ht="128.5" customHeight="1">
+    <row r="22" ht="142" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>CCP 5</t>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Raw or undercooked fish (crudo, ceviche, tartare) — parasite destruction (FDA Food Code 3-402.11): frozen and stored at −4 °F or below for 7 days, or frozen at −31 °F or below until solid and stored at −31 °F or below for 15 h, or frozen at −31 °F or below until solid and stored at −4 °F or below for 24 h; keep the record 90 days (FDA Food Code 3-402.12) and the consumer advisory on the menu (FDA Food Code 3-603.11)</t>
+          <t>Raw or undercooked fish (crudo, ceviche, tartare) — parasite destruction (FDA Food Code 3-402.11; some species are exempt, see 3-402.11(B)): frozen and stored at −4 °F or below for 7 days, or frozen at −31 °F or below until solid and stored at −31 °F or below for 15 h, or frozen at −31 °F or below until solid and stored at −4 °F or below for 24 h; keep the record 90 days (FDA Food Code 3-402.12) and the consumer advisory on the menu (FDA Food Code 3-603.11)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
